--- a/Agent_Harness_Types_Comparison.xlsx
+++ b/Agent_Harness_Types_Comparison.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Performance Benchmarks" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Market Projections" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Funding &amp; Valuation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources &amp; Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Token Usage by Harness" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sources &amp; Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +47,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -86,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -100,6 +107,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3330,7 +3338,857 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Token Consumption &amp; Cost Impact by Agent Harness Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Framework / Harness</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Token Overhead vs. Raw API</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Primary Overhead Source</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Cost per 1K Tasks (GPT-4o)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Multi-Agent Multiplier</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Context Mgmt Strategy</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Token Savings from Mgmt</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Annual Cost (100K tasks/mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>+9%</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>State serialization; minimal wrapper</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>$41.70</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>3–8× (sub-graphs most efficient)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Autonomous compression; trimming; summarization; checkpointing</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>60–80%</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>$135K</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CrewAI</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>+18%</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Role prompts; delegation instructions; crew coordination</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>$48.20</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>3–5× (manager + workers)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Shared context window; manager summarization between handoffs</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>20–40%</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>$360K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>AutoGen (legacy)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>+31%</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Conversational message passing; bilateral agent-to-agent messages</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>$67.40</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>5–10× (all agents read all messages)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Full conversation replay; no built-in compression</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0% (none)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>OpenAI Agents SDK</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>~+12% (est.)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Handoff context; guardrail checks; tracing metadata</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Model-dependent</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1.5–2× (handoff pairs)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Per-agent context isolation; handoff transfers relevant state</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>30–50%</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>$210K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Claude Agent SDK</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>~+8–15% (est.)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Tool-use loop; tool results can be large (files, shell output)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Model-dependent</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1× (primarily single-agent)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Conversation + tool results; relies on model context window</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>0–20%</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Google ADK</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>~+10–15% (est.)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Model-driven planning; session management overhead</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Model-dependent</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2–4× (A2A protocol)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Sessions + Memory Bank; automatic session compaction</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>40–60%</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Strands Agents</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>~+10% (est.)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Minimal orchestration; model-driven planning</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Model-dependent</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2–3× (handoffs + swarms)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Session-based; handoff with condensed context</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>30–50%</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Salesforce Agentforce</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Abstracted</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Token costs hidden; $2/conversation or $0.10/action</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>$2.00/conversation</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>N/A (managed)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Managed by platform; no user control</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>$2.4M (per-conversation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Token Anatomy: Where Tokens Go in a Typical 10-Step Agent Task</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Token Category</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Tokens per Call</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Calls (10-step)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Total Tokens</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Cost Driver</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>System prompt</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>1,500–4,000</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>15,000–40,000</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>10–15%</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Repeated every call; fixed cost per framework</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Tool / function schemas</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2,000–5,000</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>20,000–50,000</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>12–18%</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Grows with number of tools registered</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Conversation history</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2,500 → 26,500</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>~145,000</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>40–50%</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic growth; largest cost component</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Tool results</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>200–3,000</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2,000–30,000</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>5–12%</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Highly variable; file reads / web fetches can be massive</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Thinking / reasoning tokens</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>3–10× output</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>30,000–100,000+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>15–30%</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning models only (o3, o4-mini, Opus 4); invisible but billed</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Output tokens</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>200–800</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2,000–8,000</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>3–5%</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>3–8× more expensive per token than input</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Multi-Agent Topology Token Multipliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Topology</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Token Multiplier vs. Single Agent</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Best Framework Fit</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Single agent (tool loop)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>1× (baseline)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>One context window, one loop</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Claude Agent SDK, LangGraph</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sequential handoff (2 agents)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>1.5–2×</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Handoff transfers condensed context; second agent builds new history</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>OpenAI Agents SDK, Strands</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Parallel fan-out (3 agents)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2.5–3.5×</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Each agent runs independently; results merged by orchestrator</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>LangGraph, Google ADK</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Crew with manager (4 agents)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>3–5×</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Manager delegates + reviews; each worker has full context cycle</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>CrewAI</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Conversational swarm (4+ agents)</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>5–10×</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>All agents read all messages; bilateral token costs; negotiation rounds</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>AutoGen (legacy)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Hierarchical sub-graphs (nested)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>3–8×</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Sub-graphs encapsulate; parent only sees summaries; most efficient multi-agent</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3455,22 +4313,46 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Token Overhead Benchmarks</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Frameworks categorized by: (1) open-source vs. proprietary, (2) standalone vs. platform-embedded, (3) architecture pattern, (4) target user persona. Categories are non-exclusive.</t>
+          <t>Multi-Agent Orchestration Frameworks Benchmark (agent-harness.ai); TokenMix framework comparison 2026; AI Cost Check agent cost guide 2026; Zylos Research token economics report (Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Token Anatomy &amp; Multipliers</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Context Window Budgeting (gantz.ai); ContextBudget paper (arXiv 2604.01664); Augment Code loop cost model; LangChain autonomous context compression blog; Salesforce Agentforce pricing page (salesforce.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Frameworks categorized by: (1) open-source vs. proprietary, (2) standalone vs. platform-embedded, (3) architecture pattern, (4) target user persona. Categories are non-exclusive. Token overhead measured vs. equivalent raw API calls on same model. Annual cost estimates assume 100K tasks/mo on GPT-4o pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>Disclaimers</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Estimates marked (est.) are author projections based on available data. Market size figures vary widely across analysts due to differing category definitions. GitHub stars ≠ adoption. Download counts may include CI/CD bots. This is for informational purposes and is not investment advice.</t>
         </is>
